--- a/SS/01 Foundations/R1-P1-T1-Intro-VaR-v2.xlsx
+++ b/SS/01 Foundations/R1-P1-T1-Intro-VaR-v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beall\Documents\FRM\SS\01 Foundations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC6F209-B6E3-4CF2-B39F-C0DA4636138C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DDCF27E-21C7-47FE-A56C-006AC9136932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="R1-TOC" sheetId="15" r:id="rId1"/>
@@ -109,6 +109,7 @@
     <definedName name="window">'T1.1-HSVaR'!$C$9:$C$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1340,64 +1341,64 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
-                  <c:v>5.6342882982708077E-3</c:v>
+                  <c:v>-6.4278469019770496E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-3.6361886178038573E-4</c:v>
+                  <c:v>-7.6336218814414703E-3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-2.1538018013145966E-3</c:v>
+                  <c:v>8.6220355698296159E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.6754929838451887E-3</c:v>
+                  <c:v>-1.2260400187253551E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3334259325157185E-2</c:v>
+                  <c:v>1.5887484153923827E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-5.028727546514857E-3</c:v>
+                  <c:v>9.9926025998835362E-4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.452369076151574E-3</c:v>
+                  <c:v>-1.295452974642504E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.8396898834748094E-3</c:v>
+                  <c:v>2.0314634821721706E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-4.620530845756041E-3</c:v>
+                  <c:v>-6.665977078950489E-4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-1.6993647047098794E-2</c:v>
+                  <c:v>1.0390106265415524E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-1.7710327598297902E-2</c:v>
+                  <c:v>-8.3406655565289051E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-2.510880557985813E-3</c:v>
+                  <c:v>-9.3912355719994785E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.932993594712859E-3</c:v>
+                  <c:v>-1.2280825769291051E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1601629290151506E-2</c:v>
+                  <c:v>1.7187688564620433E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3.6140205618154391E-3</c:v>
+                  <c:v>-1.4725430921510539E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.4882263543142764E-3</c:v>
+                  <c:v>-1.380910407868299E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.5407137084364714E-3</c:v>
+                  <c:v>9.6675000639854739E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.861014913266856E-3</c:v>
+                  <c:v>1.18949963766027E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8.4074609895808446E-3</c:v>
+                  <c:v>-5.2627703414215455E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-1.8918253461229263E-2</c:v>
+                  <c:v>5.224904884384658E-4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3504,7 +3505,7 @@
       </c>
       <c r="I6" s="98">
         <f ca="1">SMALL(window,(1-confidence)*n)</f>
-        <v>-1.8918253461229263E-2</v>
+        <v>-1.4725430921510539E-2</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.25">
@@ -3517,7 +3518,7 @@
       </c>
       <c r="I7" s="98">
         <f ca="1">SMALL(window,(1-confidence)*n+1)</f>
-        <v>-1.7710327598297902E-2</v>
+        <v>-1.380910407868299E-2</v>
       </c>
       <c r="J7" s="18"/>
     </row>
@@ -3538,18 +3539,18 @@
       </c>
       <c r="C9" s="20">
         <f t="shared" ref="C9:C28" ca="1" si="0">NORMINV(RAND(),0,sigma)</f>
-        <v>5.6342882982708077E-3</v>
+        <v>-6.4278469019770496E-3</v>
       </c>
       <c r="D9" s="20">
         <f t="shared" ref="D9:D28" ca="1" si="1">SMALL(window,B9)</f>
-        <v>-1.8918253461229263E-2</v>
+        <v>-1.4725430921510539E-2</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>119</v>
       </c>
       <c r="I9" s="99">
         <f ca="1">PERCENTILE(window,significance)</f>
-        <v>-1.7770723891444469E-2</v>
+        <v>-1.3854920420824366E-2</v>
       </c>
       <c r="J9" s="1" t="str">
         <f>" =PERCENTILE(window, "&amp;TEXT(significance,"0.0%")&amp;")"</f>
@@ -3562,18 +3563,18 @@
       </c>
       <c r="C10" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-3.6361886178038573E-4</v>
+        <v>-7.6336218814414703E-3</v>
       </c>
       <c r="D10" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.7710327598297902E-2</v>
+        <v>-1.380910407868299E-2</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>120</v>
       </c>
       <c r="I10" s="99">
         <f ca="1">SMALL(window,significance*n+1)</f>
-        <v>-1.7710327598297902E-2</v>
+        <v>-1.380910407868299E-2</v>
       </c>
       <c r="J10" s="1" t="str">
         <f ca="1">" =SMALL(window, "&amp;TEXT(significance,"0.0%")&amp;"*"&amp;TEXT(n,"0")&amp;"+1)"</f>
@@ -3586,22 +3587,22 @@
       </c>
       <c r="C11" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-2.1538018013145966E-3</v>
+        <v>8.6220355698296159E-3</v>
       </c>
       <c r="D11" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-1.6993647047098794E-2</v>
+        <v>-9.3912355719994785E-3</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>121</v>
       </c>
       <c r="I11" s="100">
         <f ca="1">AVERAGE(I6:I7)</f>
-        <v>-1.8314290529763584E-2</v>
+        <v>-1.4267267500096764E-2</v>
       </c>
       <c r="J11" s="1" t="str">
         <f ca="1">" =AVERAGE("&amp;TEXT(I6,"0.000%")&amp;", "&amp;TEXT(I7,"0.000%")&amp;")"</f>
-        <v xml:space="preserve"> =AVERAGE(-1.892%, -1.771%)</v>
+        <v xml:space="preserve"> =AVERAGE(-1.473%, -1.381%)</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
@@ -3610,11 +3611,11 @@
       </c>
       <c r="C12" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>1.6754929838451887E-3</v>
+        <v>-1.2260400187253551E-3</v>
       </c>
       <c r="D12" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-5.028727546514857E-3</v>
+        <v>-8.3406655565289051E-3</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
@@ -3623,11 +3624,11 @@
       </c>
       <c r="C13" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>1.3334259325157185E-2</v>
+        <v>1.5887484153923827E-3</v>
       </c>
       <c r="D13" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-4.620530845756041E-3</v>
+        <v>-7.6336218814414703E-3</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
@@ -3636,11 +3637,11 @@
       </c>
       <c r="C14" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-5.028727546514857E-3</v>
+        <v>9.9926025998835362E-4</v>
       </c>
       <c r="D14" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.510880557985813E-3</v>
+        <v>-6.4278469019770496E-3</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -3649,11 +3650,11 @@
       </c>
       <c r="C15" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>2.452369076151574E-3</v>
+        <v>-1.295452974642504E-3</v>
       </c>
       <c r="D15" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-2.1538018013145966E-3</v>
+        <v>-5.2627703414215455E-3</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -3662,11 +3663,11 @@
       </c>
       <c r="C16" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>1.8396898834748094E-3</v>
+        <v>2.0314634821721706E-2</v>
       </c>
       <c r="D16" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>-3.6361886178038573E-4</v>
+        <v>-1.295452974642504E-3</v>
       </c>
       <c r="I16" s="18"/>
     </row>
@@ -3676,11 +3677,11 @@
       </c>
       <c r="C17" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-4.620530845756041E-3</v>
+        <v>-6.665977078950489E-4</v>
       </c>
       <c r="D17" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.6754929838451887E-3</v>
+        <v>-1.2280825769291051E-3</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
@@ -3689,11 +3690,11 @@
       </c>
       <c r="C18" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.6993647047098794E-2</v>
+        <v>1.0390106265415524E-2</v>
       </c>
       <c r="D18" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.8396898834748094E-3</v>
+        <v>-1.2260400187253551E-3</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
@@ -3702,11 +3703,11 @@
       </c>
       <c r="C19" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.7710327598297902E-2</v>
+        <v>-8.3406655565289051E-3</v>
       </c>
       <c r="D19" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.861014913266856E-3</v>
+        <v>-6.665977078950489E-4</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
@@ -3715,11 +3716,11 @@
       </c>
       <c r="C20" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-2.510880557985813E-3</v>
+        <v>-9.3912355719994785E-3</v>
       </c>
       <c r="D20" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>2.452369076151574E-3</v>
+        <v>5.224904884384658E-4</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -3728,11 +3729,11 @@
       </c>
       <c r="C21" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>8.932993594712859E-3</v>
+        <v>-1.2280825769291051E-3</v>
       </c>
       <c r="D21" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>2.5407137084364714E-3</v>
+        <v>9.9926025998835362E-4</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
@@ -3741,11 +3742,11 @@
       </c>
       <c r="C22" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>1.1601629290151506E-2</v>
+        <v>1.7187688564620433E-2</v>
       </c>
       <c r="D22" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>3.6140205618154391E-3</v>
+        <v>1.5887484153923827E-3</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
@@ -3754,11 +3755,11 @@
       </c>
       <c r="C23" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>3.6140205618154391E-3</v>
+        <v>-1.4725430921510539E-2</v>
       </c>
       <c r="D23" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>5.4882263543142764E-3</v>
+        <v>8.6220355698296159E-3</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
@@ -3767,11 +3768,11 @@
       </c>
       <c r="C24" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>5.4882263543142764E-3</v>
+        <v>-1.380910407868299E-2</v>
       </c>
       <c r="D24" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>5.6342882982708077E-3</v>
+        <v>9.6675000639854739E-3</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
@@ -3780,11 +3781,11 @@
       </c>
       <c r="C25" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>2.5407137084364714E-3</v>
+        <v>9.6675000639854739E-3</v>
       </c>
       <c r="D25" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>8.4074609895808446E-3</v>
+        <v>1.0390106265415524E-2</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
@@ -3793,11 +3794,11 @@
       </c>
       <c r="C26" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>1.861014913266856E-3</v>
+        <v>1.18949963766027E-2</v>
       </c>
       <c r="D26" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>8.932993594712859E-3</v>
+        <v>1.18949963766027E-2</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.25">
@@ -3806,11 +3807,11 @@
       </c>
       <c r="C27" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>8.4074609895808446E-3</v>
+        <v>-5.2627703414215455E-3</v>
       </c>
       <c r="D27" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.1601629290151506E-2</v>
+        <v>1.7187688564620433E-2</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
@@ -3819,11 +3820,11 @@
       </c>
       <c r="C28" s="20">
         <f t="shared" ca="1" si="0"/>
-        <v>-1.8918253461229263E-2</v>
+        <v>5.224904884384658E-4</v>
       </c>
       <c r="D28" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>1.3334259325157185E-2</v>
+        <v>2.0314634821721706E-2</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
@@ -4645,15 +4646,15 @@
         <v>-100</v>
       </c>
       <c r="N10" s="43">
-        <f t="shared" ref="N10:N12" si="0">J10*(1+$N$4)^I10/(1+$N$5)^I10</f>
+        <f>J10*(1+$N$4)^I10/(1+$N$5)^I10</f>
         <v>-100</v>
       </c>
       <c r="O10" s="43">
-        <f t="shared" ref="O10:O12" si="1">N10/(1+$N$4)^I10</f>
+        <f>N10/(1+$N$4)^I10</f>
         <v>-100</v>
       </c>
       <c r="P10" s="44" t="str">
-        <f t="shared" ref="P10:P12" si="2">TEXT(N10,"$#,###")&amp;"= "&amp;TEXT(J10,"$#,###")&amp;" * (1+"&amp;TEXT($N$4,"#.00%")&amp;")^"&amp;I10&amp;" / "&amp;"(1+"&amp;TEXT($N$5,"#.00%")&amp;")^"&amp;I10</f>
+        <f>TEXT(N10,"$#,###")&amp;"= "&amp;TEXT(J10,"$#,###")&amp;" * (1+"&amp;TEXT($N$4,"#.00%")&amp;")^"&amp;I10&amp;" / "&amp;"(1+"&amp;TEXT($N$5,"#.00%")&amp;")^"&amp;I10</f>
         <v>-$100= -$100 * (1+2.00%)^0 / (1+9.86%)^0</v>
       </c>
       <c r="T10" s="29"/>
@@ -4668,19 +4669,19 @@
       </c>
       <c r="K11" s="43"/>
       <c r="L11" s="43">
-        <f t="shared" ref="L11:L12" si="3">J11/(1+$N$5)^I11</f>
+        <f>J11/(1+$N$5)^I11</f>
         <v>45.512470416894232</v>
       </c>
       <c r="N11" s="43">
-        <f t="shared" si="0"/>
+        <f>J11*(1+$N$4)^I11/(1+$N$5)^I11</f>
         <v>46.422719825232114</v>
       </c>
       <c r="O11" s="43">
-        <f t="shared" si="1"/>
+        <f>N11/(1+$N$4)^I11</f>
         <v>45.512470416894232</v>
       </c>
       <c r="P11" s="44" t="str">
-        <f t="shared" si="2"/>
+        <f>TEXT(N11,"$#,###")&amp;"= "&amp;TEXT(J11,"$#,###")&amp;" * (1+"&amp;TEXT($N$4,"#.00%")&amp;")^"&amp;I11&amp;" / "&amp;"(1+"&amp;TEXT($N$5,"#.00%")&amp;")^"&amp;I11</f>
         <v>$46= $50 * (1+2.00%)^1 / (1+9.86%)^1</v>
       </c>
       <c r="T11" s="29"/>
@@ -4702,19 +4703,19 @@
       </c>
       <c r="K12" s="43"/>
       <c r="L12" s="43">
-        <f t="shared" si="3"/>
+        <f>J12/(1+$N$5)^I12</f>
         <v>57.998778976562825</v>
       </c>
       <c r="N12" s="43">
-        <f t="shared" si="0"/>
+        <f>J12*(1+$N$4)^I12/(1+$N$5)^I12</f>
         <v>60.341929647215963</v>
       </c>
       <c r="O12" s="43">
-        <f t="shared" si="1"/>
+        <f>N12/(1+$N$4)^I12</f>
         <v>57.998778976562825</v>
       </c>
       <c r="P12" s="44" t="str">
-        <f t="shared" si="2"/>
+        <f>TEXT(N12,"$#,###")&amp;"= "&amp;TEXT(J12,"$#,###")&amp;" * (1+"&amp;TEXT($N$4,"#.00%")&amp;")^"&amp;I12&amp;" / "&amp;"(1+"&amp;TEXT($N$5,"#.00%")&amp;")^"&amp;I12</f>
         <v>$60= $70 * (1+2.00%)^2 / (1+9.86%)^2</v>
       </c>
       <c r="T12" s="29"/>
